--- a/backend/data/financials_by_company/0710.HK.xlsx
+++ b/backend/data/financials_by_company/0710.HK.xlsx
@@ -692,650 +692,650 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1731654.700053</v>
+        <v>-628961.996564</v>
       </c>
       <c r="C2" t="n">
-        <v>0.048582</v>
+        <v>0.111736</v>
       </c>
       <c r="D2" t="n">
-        <v>650174000</v>
+        <v>518714000</v>
       </c>
       <c r="E2" t="n">
-        <v>35644000</v>
+        <v>-5629000</v>
       </c>
       <c r="F2" t="n">
-        <v>35644000</v>
+        <v>-5629000</v>
       </c>
       <c r="G2" t="n">
-        <v>391282000</v>
+        <v>327798000</v>
       </c>
       <c r="H2" t="n">
-        <v>248365000</v>
+        <v>163491000</v>
       </c>
       <c r="I2" t="n">
-        <v>11178266000</v>
+        <v>6337217000</v>
       </c>
       <c r="J2" t="n">
-        <v>685818000</v>
+        <v>513085000</v>
       </c>
       <c r="K2" t="n">
-        <v>437453000</v>
+        <v>349594000</v>
       </c>
       <c r="L2" t="n">
-        <v>94777000</v>
+        <v>23049000</v>
       </c>
       <c r="M2" t="n">
-        <v>15362000</v>
+        <v>915000</v>
       </c>
       <c r="N2" t="n">
-        <v>115440000</v>
+        <v>25403000</v>
       </c>
       <c r="O2" t="n">
-        <v>357369654.700053</v>
+        <v>332798038.003436</v>
       </c>
       <c r="P2" t="n">
-        <v>391282000</v>
+        <v>327798000</v>
       </c>
       <c r="Q2" t="n">
-        <v>13155233000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>11127000</v>
-      </c>
+        <v>7430945000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>437453000</v>
+        <v>350084000</v>
       </c>
       <c r="T2" t="n">
-        <v>790536366</v>
+        <v>732457164</v>
       </c>
       <c r="U2" t="n">
-        <v>788571961</v>
+        <v>727080789</v>
       </c>
       <c r="V2" t="n">
-        <v>0.495</v>
+        <v>0.448</v>
       </c>
       <c r="W2" t="n">
-        <v>0.496</v>
+        <v>0.451</v>
       </c>
       <c r="X2" t="n">
-        <v>391282000</v>
+        <v>327798000</v>
       </c>
       <c r="Y2" t="n">
-        <v>391282000</v>
+        <v>327798000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>391282000</v>
+        <v>327798000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-10303000</v>
+        <v>18079000</v>
       </c>
       <c r="AC2" t="n">
-        <v>401585000</v>
+        <v>309719000</v>
       </c>
       <c r="AD2" t="n">
-        <v>401585000</v>
+        <v>309719000</v>
       </c>
       <c r="AE2" t="n">
-        <v>20506000</v>
+        <v>38960000</v>
       </c>
       <c r="AF2" t="n">
-        <v>422091000</v>
+        <v>348679000</v>
       </c>
       <c r="AG2" t="n">
-        <v>25000</v>
+        <v>14594000</v>
       </c>
       <c r="AH2" t="n">
-        <v>27300000</v>
+        <v>-3909000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-27300000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>1488000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2421000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>94777000</v>
+        <v>23049000</v>
       </c>
       <c r="AL2" t="n">
-        <v>5301000</v>
+        <v>1439000</v>
       </c>
       <c r="AM2" t="n">
-        <v>15362000</v>
+        <v>915000</v>
       </c>
       <c r="AN2" t="n">
-        <v>115440000</v>
+        <v>25403000</v>
       </c>
       <c r="AO2" t="n">
-        <v>293273000</v>
+        <v>306998000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1976967000</v>
+        <v>1093728000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>394411000</v>
+        <v>234802000</v>
       </c>
       <c r="AR2" t="n">
-        <v>248365000</v>
+        <v>163491000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4064000</v>
+        <v>3757000</v>
       </c>
       <c r="AT2" t="n">
-        <v>244301000</v>
+        <v>159734000</v>
       </c>
       <c r="AU2" t="n">
-        <v>256204000</v>
+        <v>119475000</v>
       </c>
       <c r="AV2" t="n">
-        <v>227238000</v>
+        <v>94582000</v>
       </c>
       <c r="AW2" t="n">
-        <v>28966000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11127000</v>
-      </c>
+        <v>24893000</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>2270240000</v>
+        <v>1400726000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11178266000</v>
+        <v>6337217000</v>
       </c>
       <c r="BA2" t="n">
-        <v>13448506000</v>
+        <v>7737943000</v>
       </c>
       <c r="BB2" t="n">
-        <v>13448506000</v>
+        <v>7737943000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>108288.753259</v>
+        <v>36686.766609</v>
       </c>
       <c r="C3" t="n">
-        <v>0.109162</v>
+        <v>0.149133</v>
       </c>
       <c r="D3" t="n">
-        <v>769523000</v>
+        <v>840830000</v>
       </c>
       <c r="E3" t="n">
-        <v>992000</v>
+        <v>246000</v>
       </c>
       <c r="F3" t="n">
-        <v>992000</v>
+        <v>246000</v>
       </c>
       <c r="G3" t="n">
-        <v>475260000</v>
+        <v>582451000</v>
       </c>
       <c r="H3" t="n">
-        <v>205263000</v>
+        <v>171068000</v>
       </c>
       <c r="I3" t="n">
-        <v>8758277000</v>
+        <v>8905076000</v>
       </c>
       <c r="J3" t="n">
-        <v>770515000</v>
+        <v>841076000</v>
       </c>
       <c r="K3" t="n">
-        <v>565252000</v>
+        <v>670008000</v>
       </c>
       <c r="L3" t="n">
-        <v>64675000</v>
+        <v>38808000</v>
       </c>
       <c r="M3" t="n">
-        <v>25220000</v>
+        <v>12361000</v>
       </c>
       <c r="N3" t="n">
-        <v>93282000</v>
+        <v>52849000</v>
       </c>
       <c r="O3" t="n">
-        <v>474376288.753259</v>
+        <v>582241686.766609</v>
       </c>
       <c r="P3" t="n">
-        <v>475260000</v>
+        <v>582451000</v>
       </c>
       <c r="Q3" t="n">
-        <v>10281270000</v>
+        <v>10134274000</v>
       </c>
       <c r="R3" t="n">
-        <v>16150000</v>
+        <v>3766000</v>
       </c>
       <c r="S3" t="n">
-        <v>569723000</v>
+        <v>670464000</v>
       </c>
       <c r="T3" t="n">
-        <v>788953698</v>
+        <v>748648454</v>
       </c>
       <c r="U3" t="n">
-        <v>786365101</v>
+        <v>742756425</v>
       </c>
       <c r="V3" t="n">
-        <v>0.602</v>
+        <v>0.778</v>
       </c>
       <c r="W3" t="n">
-        <v>0.604</v>
+        <v>0.784</v>
       </c>
       <c r="X3" t="n">
-        <v>475260000</v>
+        <v>582451000</v>
       </c>
       <c r="Y3" t="n">
-        <v>475260000</v>
+        <v>582451000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>475260000</v>
+        <v>582451000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-5821000</v>
+        <v>22881000</v>
       </c>
       <c r="AC3" t="n">
-        <v>481081000</v>
+        <v>559570000</v>
       </c>
       <c r="AD3" t="n">
-        <v>481081000</v>
+        <v>559570000</v>
       </c>
       <c r="AE3" t="n">
-        <v>58951000</v>
+        <v>98077000</v>
       </c>
       <c r="AF3" t="n">
-        <v>540032000</v>
+        <v>657647000</v>
       </c>
       <c r="AG3" t="n">
-        <v>4212000</v>
+        <v>14122000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1708000</v>
+        <v>982000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1708000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>-982000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>64675000</v>
+        <v>38808000</v>
       </c>
       <c r="AL3" t="n">
-        <v>3387000</v>
+        <v>1680000</v>
       </c>
       <c r="AM3" t="n">
-        <v>25220000</v>
+        <v>12361000</v>
       </c>
       <c r="AN3" t="n">
-        <v>93282000</v>
+        <v>52849000</v>
       </c>
       <c r="AO3" t="n">
-        <v>479146000</v>
+        <v>588087000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1522993000</v>
+        <v>1229198000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>289265000</v>
+        <v>299810000</v>
       </c>
       <c r="AR3" t="n">
-        <v>205263000</v>
+        <v>171068000</v>
       </c>
       <c r="AS3" t="n">
-        <v>3153000</v>
+        <v>5298000</v>
       </c>
       <c r="AT3" t="n">
-        <v>202110000</v>
+        <v>165770000</v>
       </c>
       <c r="AU3" t="n">
-        <v>153747000</v>
+        <v>133973000</v>
       </c>
       <c r="AV3" t="n">
-        <v>135617000</v>
+        <v>110896000</v>
       </c>
       <c r="AW3" t="n">
-        <v>18130000</v>
+        <v>23077000</v>
       </c>
       <c r="AX3" t="n">
-        <v>16150000</v>
+        <v>3766000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2002139000</v>
+        <v>1817285000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8758277000</v>
+        <v>8905076000</v>
       </c>
       <c r="BA3" t="n">
-        <v>10760416000</v>
+        <v>10722361000</v>
       </c>
       <c r="BB3" t="n">
-        <v>10760416000</v>
+        <v>10722361000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>36686.766609</v>
+        <v>108288.753259</v>
       </c>
       <c r="C4" t="n">
-        <v>0.149133</v>
+        <v>0.109162</v>
       </c>
       <c r="D4" t="n">
-        <v>840830000</v>
+        <v>769523000</v>
       </c>
       <c r="E4" t="n">
-        <v>246000</v>
+        <v>992000</v>
       </c>
       <c r="F4" t="n">
-        <v>246000</v>
+        <v>992000</v>
       </c>
       <c r="G4" t="n">
-        <v>582451000</v>
+        <v>475260000</v>
       </c>
       <c r="H4" t="n">
-        <v>171068000</v>
+        <v>205263000</v>
       </c>
       <c r="I4" t="n">
-        <v>8905076000</v>
+        <v>8758277000</v>
       </c>
       <c r="J4" t="n">
-        <v>841076000</v>
+        <v>770515000</v>
       </c>
       <c r="K4" t="n">
-        <v>670008000</v>
+        <v>565252000</v>
       </c>
       <c r="L4" t="n">
-        <v>38808000</v>
+        <v>64675000</v>
       </c>
       <c r="M4" t="n">
-        <v>12361000</v>
+        <v>25220000</v>
       </c>
       <c r="N4" t="n">
-        <v>52849000</v>
+        <v>93282000</v>
       </c>
       <c r="O4" t="n">
-        <v>582241686.766609</v>
+        <v>474376288.753259</v>
       </c>
       <c r="P4" t="n">
-        <v>582451000</v>
+        <v>475260000</v>
       </c>
       <c r="Q4" t="n">
-        <v>10134274000</v>
+        <v>10281270000</v>
       </c>
       <c r="R4" t="n">
-        <v>3766000</v>
+        <v>16150000</v>
       </c>
       <c r="S4" t="n">
-        <v>670464000</v>
+        <v>569723000</v>
       </c>
       <c r="T4" t="n">
-        <v>748648454</v>
+        <v>788953698</v>
       </c>
       <c r="U4" t="n">
-        <v>742756425</v>
+        <v>786365101</v>
       </c>
       <c r="V4" t="n">
-        <v>0.778</v>
+        <v>0.602</v>
       </c>
       <c r="W4" t="n">
-        <v>0.784</v>
+        <v>0.604</v>
       </c>
       <c r="X4" t="n">
-        <v>582451000</v>
+        <v>475260000</v>
       </c>
       <c r="Y4" t="n">
-        <v>582451000</v>
+        <v>475260000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>582451000</v>
+        <v>475260000</v>
       </c>
       <c r="AB4" t="n">
-        <v>22881000</v>
+        <v>-5821000</v>
       </c>
       <c r="AC4" t="n">
-        <v>559570000</v>
+        <v>481081000</v>
       </c>
       <c r="AD4" t="n">
-        <v>559570000</v>
+        <v>481081000</v>
       </c>
       <c r="AE4" t="n">
-        <v>98077000</v>
+        <v>58951000</v>
       </c>
       <c r="AF4" t="n">
-        <v>657647000</v>
+        <v>540032000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14122000</v>
+        <v>4212000</v>
       </c>
       <c r="AH4" t="n">
-        <v>982000</v>
+        <v>1708000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-982000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>-1708000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>38808000</v>
+        <v>64675000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1680000</v>
+        <v>3387000</v>
       </c>
       <c r="AM4" t="n">
-        <v>12361000</v>
+        <v>25220000</v>
       </c>
       <c r="AN4" t="n">
-        <v>52849000</v>
+        <v>93282000</v>
       </c>
       <c r="AO4" t="n">
-        <v>588087000</v>
+        <v>479146000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1229198000</v>
+        <v>1522993000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>299810000</v>
+        <v>289265000</v>
       </c>
       <c r="AR4" t="n">
-        <v>171068000</v>
+        <v>205263000</v>
       </c>
       <c r="AS4" t="n">
-        <v>5298000</v>
+        <v>3153000</v>
       </c>
       <c r="AT4" t="n">
-        <v>165770000</v>
+        <v>202110000</v>
       </c>
       <c r="AU4" t="n">
-        <v>133973000</v>
+        <v>153747000</v>
       </c>
       <c r="AV4" t="n">
-        <v>110896000</v>
+        <v>135617000</v>
       </c>
       <c r="AW4" t="n">
-        <v>23077000</v>
+        <v>18130000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3766000</v>
+        <v>16150000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1817285000</v>
+        <v>2002139000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8905076000</v>
+        <v>8758277000</v>
       </c>
       <c r="BA4" t="n">
-        <v>10722361000</v>
+        <v>10760416000</v>
       </c>
       <c r="BB4" t="n">
-        <v>10722361000</v>
+        <v>10760416000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-628961.996564</v>
+        <v>1731654.700053</v>
       </c>
       <c r="C5" t="n">
-        <v>0.111736</v>
+        <v>0.048582</v>
       </c>
       <c r="D5" t="n">
-        <v>518714000</v>
+        <v>650174000</v>
       </c>
       <c r="E5" t="n">
-        <v>-5629000</v>
+        <v>35644000</v>
       </c>
       <c r="F5" t="n">
-        <v>-5629000</v>
+        <v>35644000</v>
       </c>
       <c r="G5" t="n">
-        <v>327798000</v>
+        <v>391282000</v>
       </c>
       <c r="H5" t="n">
-        <v>163491000</v>
+        <v>248365000</v>
       </c>
       <c r="I5" t="n">
-        <v>6337217000</v>
+        <v>11178266000</v>
       </c>
       <c r="J5" t="n">
-        <v>513085000</v>
+        <v>685818000</v>
       </c>
       <c r="K5" t="n">
-        <v>349594000</v>
+        <v>437453000</v>
       </c>
       <c r="L5" t="n">
-        <v>23049000</v>
+        <v>94777000</v>
       </c>
       <c r="M5" t="n">
-        <v>915000</v>
+        <v>15362000</v>
       </c>
       <c r="N5" t="n">
-        <v>25403000</v>
+        <v>115440000</v>
       </c>
       <c r="O5" t="n">
-        <v>332798038.003436</v>
+        <v>357369654.700053</v>
       </c>
       <c r="P5" t="n">
-        <v>327798000</v>
+        <v>391282000</v>
       </c>
       <c r="Q5" t="n">
-        <v>7430945000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>13155233000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>11127000</v>
+      </c>
       <c r="S5" t="n">
-        <v>350084000</v>
+        <v>437453000</v>
       </c>
       <c r="T5" t="n">
-        <v>732457164</v>
+        <v>790536366</v>
       </c>
       <c r="U5" t="n">
-        <v>727080789</v>
+        <v>788571961</v>
       </c>
       <c r="V5" t="n">
-        <v>0.448</v>
+        <v>0.495</v>
       </c>
       <c r="W5" t="n">
-        <v>0.451</v>
+        <v>0.496</v>
       </c>
       <c r="X5" t="n">
-        <v>327798000</v>
+        <v>391282000</v>
       </c>
       <c r="Y5" t="n">
-        <v>327798000</v>
+        <v>391282000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>327798000</v>
+        <v>391282000</v>
       </c>
       <c r="AB5" t="n">
-        <v>18079000</v>
+        <v>-10303000</v>
       </c>
       <c r="AC5" t="n">
-        <v>309719000</v>
+        <v>401585000</v>
       </c>
       <c r="AD5" t="n">
-        <v>309719000</v>
+        <v>401585000</v>
       </c>
       <c r="AE5" t="n">
-        <v>38960000</v>
+        <v>20506000</v>
       </c>
       <c r="AF5" t="n">
-        <v>348679000</v>
+        <v>422091000</v>
       </c>
       <c r="AG5" t="n">
-        <v>14594000</v>
+        <v>25000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3909000</v>
+        <v>27300000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1488000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2421000</v>
-      </c>
+        <v>-27300000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>23049000</v>
+        <v>94777000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1439000</v>
+        <v>5301000</v>
       </c>
       <c r="AM5" t="n">
-        <v>915000</v>
+        <v>15362000</v>
       </c>
       <c r="AN5" t="n">
-        <v>25403000</v>
+        <v>115440000</v>
       </c>
       <c r="AO5" t="n">
-        <v>306998000</v>
+        <v>293273000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1093728000</v>
+        <v>1976967000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>234802000</v>
+        <v>394411000</v>
       </c>
       <c r="AR5" t="n">
-        <v>163491000</v>
+        <v>248365000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3757000</v>
+        <v>4064000</v>
       </c>
       <c r="AT5" t="n">
-        <v>159734000</v>
+        <v>244301000</v>
       </c>
       <c r="AU5" t="n">
-        <v>119475000</v>
+        <v>256204000</v>
       </c>
       <c r="AV5" t="n">
-        <v>94582000</v>
+        <v>227238000</v>
       </c>
       <c r="AW5" t="n">
-        <v>24893000</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>28966000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11127000</v>
+      </c>
       <c r="AY5" t="n">
-        <v>1400726000</v>
+        <v>2270240000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6337217000</v>
+        <v>11178266000</v>
       </c>
       <c r="BA5" t="n">
-        <v>7737943000</v>
+        <v>13448506000</v>
       </c>
       <c r="BB5" t="n">
-        <v>7737943000</v>
+        <v>13448506000</v>
       </c>
     </row>
   </sheetData>
@@ -1721,864 +1721,864 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>12373000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>779202204</v>
+        <v>736155000</v>
       </c>
       <c r="D2" t="n">
-        <v>791575204</v>
+        <v>736155000</v>
       </c>
       <c r="E2" t="n">
-        <v>410692000</v>
+        <v>22555000</v>
       </c>
       <c r="F2" t="n">
-        <v>4505858000</v>
+        <v>2982480000</v>
       </c>
       <c r="G2" t="n">
-        <v>4911072000</v>
+        <v>3032424000</v>
       </c>
       <c r="H2" t="n">
-        <v>2695701000</v>
+        <v>2685133000</v>
       </c>
       <c r="I2" t="n">
-        <v>4505858000</v>
+        <v>2982480000</v>
       </c>
       <c r="J2" t="n">
-        <v>34906000</v>
+        <v>22555000</v>
       </c>
       <c r="K2" t="n">
-        <v>4535286000</v>
+        <v>3032424000</v>
       </c>
       <c r="L2" t="n">
-        <v>4705750000</v>
+        <v>3032424000</v>
       </c>
       <c r="M2" t="n">
-        <v>4600495000</v>
+        <v>3345625000</v>
       </c>
       <c r="N2" t="n">
-        <v>65209000</v>
+        <v>313201000</v>
       </c>
       <c r="O2" t="n">
-        <v>4535286000</v>
+        <v>3032424000</v>
       </c>
       <c r="P2" t="n">
-        <v>-15652000</v>
+        <v>-33609000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2159062000</v>
+        <v>680322000</v>
       </c>
       <c r="R2" t="n">
-        <v>2382139000</v>
+        <v>2030037000</v>
       </c>
       <c r="S2" t="n">
-        <v>197894000</v>
+        <v>184039000</v>
       </c>
       <c r="T2" t="n">
-        <v>197894000</v>
+        <v>184039000</v>
       </c>
       <c r="U2" t="n">
-        <v>6864447000</v>
+        <v>2197539000</v>
       </c>
       <c r="V2" t="n">
-        <v>364846000</v>
+        <v>29486000</v>
       </c>
       <c r="W2" t="n">
-        <v>171821000</v>
+        <v>5279000</v>
       </c>
       <c r="X2" t="n">
-        <v>2448000</v>
+        <v>13165000</v>
       </c>
       <c r="Y2" t="n">
-        <v>190577000</v>
+        <v>11042000</v>
       </c>
       <c r="Z2" t="n">
-        <v>20113000</v>
+        <v>11042000</v>
       </c>
       <c r="AA2" t="n">
-        <v>170464000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>6499601000</v>
+        <v>2168053000</v>
       </c>
       <c r="AC2" t="n">
-        <v>220115000</v>
+        <v>11513000</v>
       </c>
       <c r="AD2" t="n">
-        <v>14793000</v>
+        <v>11513000</v>
       </c>
       <c r="AE2" t="n">
-        <v>205322000</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>5390498000</v>
+        <v>1669335000</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>23272000</v>
+        <v>17476000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5367226000</v>
+        <v>1651859000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11464942000</v>
+        <v>5543164000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2269640000</v>
+        <v>689978000</v>
       </c>
       <c r="AL2" t="n">
-        <v>38822000</v>
+        <v>15332000</v>
       </c>
       <c r="AM2" t="n">
-        <v>59718000</v>
+        <v>654000</v>
       </c>
       <c r="AN2" t="n">
-        <v>40186000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>38486000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>40614000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>29428000</v>
+        <v>49944000</v>
       </c>
       <c r="AT2" t="n">
-        <v>29428000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>38457000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11487000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>2060385000</v>
+        <v>583434000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1770004000</v>
+        <v>-1679395000</v>
       </c>
       <c r="AX2" t="n">
-        <v>3830389000</v>
+        <v>2262829000</v>
       </c>
       <c r="AY2" t="n">
-        <v>124578000</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>172741000</v>
+        <v>206626000</v>
       </c>
       <c r="BA2" t="n">
-        <v>2722861000</v>
+        <v>1732858000</v>
       </c>
       <c r="BB2" t="n">
-        <v>51828000</v>
+        <v>31571000</v>
       </c>
       <c r="BC2" t="n">
-        <v>758381000</v>
+        <v>291774000</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>9195302000</v>
+        <v>4853186000</v>
       </c>
       <c r="BF2" t="n">
-        <v>48717000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>147326000</v>
-      </c>
+        <v>50180000</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>104656000</v>
+        <v>51324000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1778379000</v>
+        <v>832617000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>790882000</v>
+        <v>416455000</v>
       </c>
       <c r="BK2" t="n">
-        <v>409565000</v>
+        <v>128402000</v>
       </c>
       <c r="BL2" t="n">
-        <v>577932000</v>
+        <v>287760000</v>
       </c>
       <c r="BM2" t="n">
-        <v>57587000</v>
+        <v>26607000</v>
       </c>
       <c r="BN2" t="n">
-        <v>229354000</v>
+        <v>4740000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2895566000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
+        <v>1616233000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-10642000</v>
+      </c>
       <c r="BQ2" t="n">
-        <v>2895566000</v>
+        <v>1616233000</v>
       </c>
       <c r="BR2" t="n">
-        <v>3933717000</v>
+        <v>2271485000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1233576000</v>
+        <v>4367000</v>
       </c>
       <c r="BT2" t="n">
-        <v>2700141000</v>
+        <v>2267118000</v>
       </c>
       <c r="BU2" t="n">
-        <v>671473000</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>2028668000</v>
+        <v>2267118000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>12373000</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>779202204</v>
+        <v>791410204</v>
       </c>
       <c r="D3" t="n">
-        <v>791575204</v>
+        <v>791410204</v>
       </c>
       <c r="E3" t="n">
-        <v>642002000</v>
+        <v>678994000</v>
       </c>
       <c r="F3" t="n">
-        <v>4328534000</v>
+        <v>4042525000</v>
       </c>
       <c r="G3" t="n">
-        <v>4973531000</v>
+        <v>4731898000</v>
       </c>
       <c r="H3" t="n">
-        <v>3074434000</v>
+        <v>2507441000</v>
       </c>
       <c r="I3" t="n">
-        <v>4328534000</v>
+        <v>4042525000</v>
       </c>
       <c r="J3" t="n">
-        <v>22066000</v>
+        <v>11794000</v>
       </c>
       <c r="K3" t="n">
-        <v>4353595000</v>
+        <v>4064698000</v>
       </c>
       <c r="L3" t="n">
-        <v>4737092000</v>
+        <v>4095610000</v>
       </c>
       <c r="M3" t="n">
-        <v>4409711000</v>
+        <v>4115773000</v>
       </c>
       <c r="N3" t="n">
-        <v>56116000</v>
+        <v>51075000</v>
       </c>
       <c r="O3" t="n">
-        <v>4353595000</v>
+        <v>4064698000</v>
       </c>
       <c r="P3" t="n">
-        <v>-13763000</v>
+        <v>-23835000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1787999000</v>
+        <v>1302272000</v>
       </c>
       <c r="R3" t="n">
-        <v>2531799000</v>
+        <v>2712371000</v>
       </c>
       <c r="S3" t="n">
-        <v>197894000</v>
+        <v>197853000</v>
       </c>
       <c r="T3" t="n">
-        <v>197894000</v>
+        <v>197853000</v>
       </c>
       <c r="U3" t="n">
-        <v>5624159000</v>
+        <v>4167327000</v>
       </c>
       <c r="V3" t="n">
-        <v>601368000</v>
+        <v>64202000</v>
       </c>
       <c r="W3" t="n">
-        <v>200496000</v>
+        <v>18911000</v>
       </c>
       <c r="X3" t="n">
-        <v>3468000</v>
+        <v>9977000</v>
       </c>
       <c r="Y3" t="n">
-        <v>397404000</v>
+        <v>35314000</v>
       </c>
       <c r="Z3" t="n">
-        <v>13907000</v>
+        <v>4402000</v>
       </c>
       <c r="AA3" t="n">
-        <v>383497000</v>
+        <v>30912000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5022791000</v>
+        <v>4103125000</v>
       </c>
       <c r="AC3" t="n">
-        <v>244598000</v>
+        <v>643680000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8159000</v>
+        <v>7392000</v>
       </c>
       <c r="AE3" t="n">
-        <v>236439000</v>
+        <v>636288000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3822106000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>3005421000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>13925000</v>
+        <v>65324000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3808181000</v>
+        <v>2940097000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10033870000</v>
+        <v>8283100000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1936645000</v>
+        <v>1672534000</v>
       </c>
       <c r="AL3" t="n">
-        <v>101264000</v>
+        <v>98265000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8843000</v>
+        <v>11286000</v>
       </c>
       <c r="AN3" t="n">
-        <v>41897000</v>
+        <v>42588000</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>41897000</v>
+        <v>42588000</v>
       </c>
       <c r="AQ3" t="n">
+        <v>7922000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7922000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>22173000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>22173000</v>
+      </c>
+      <c r="AU3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>25061000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>25061000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>1759580000</v>
+        <v>1490300000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1831484000</v>
+        <v>-1717338000</v>
       </c>
       <c r="AX3" t="n">
-        <v>3591064000</v>
+        <v>3207638000</v>
       </c>
       <c r="AY3" t="n">
-        <v>22035000</v>
+        <v>885713000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>172567000</v>
+        <v>152099000</v>
       </c>
       <c r="BA3" t="n">
-        <v>2638682000</v>
+        <v>1804769000</v>
       </c>
       <c r="BB3" t="n">
-        <v>37385000</v>
+        <v>31822000</v>
       </c>
       <c r="BC3" t="n">
-        <v>720395000</v>
+        <v>333235000</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>8097225000</v>
+        <v>6610566000</v>
       </c>
       <c r="BF3" t="n">
-        <v>47546000</v>
+        <v>23449000</v>
       </c>
       <c r="BG3" t="n">
-        <v>55884000</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>60242000</v>
+        <v>61704000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1947101000</v>
+        <v>1568001000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>907939000</v>
+        <v>649308000</v>
       </c>
       <c r="BK3" t="n">
-        <v>571548000</v>
+        <v>281089000</v>
       </c>
       <c r="BL3" t="n">
-        <v>467614000</v>
+        <v>637604000</v>
       </c>
       <c r="BM3" t="n">
-        <v>138725000</v>
+        <v>61318000</v>
       </c>
       <c r="BN3" t="n">
-        <v>120161000</v>
+        <v>9510000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2211401000</v>
+        <v>2005973000</v>
       </c>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>2211401000</v>
+        <v>2005973000</v>
       </c>
       <c r="BR3" t="n">
-        <v>3516165000</v>
+        <v>2880611000</v>
       </c>
       <c r="BS3" t="n">
-        <v>15405000</v>
+        <v>61788000</v>
       </c>
       <c r="BT3" t="n">
-        <v>3500760000</v>
+        <v>2818823000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1258701000</v>
+        <v>777167000</v>
       </c>
       <c r="BV3" t="n">
-        <v>2242059000</v>
+        <v>2041656000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>12373000</v>
+      </c>
       <c r="C4" t="n">
-        <v>791410204</v>
+        <v>779202204</v>
       </c>
       <c r="D4" t="n">
-        <v>791410204</v>
+        <v>791575204</v>
       </c>
       <c r="E4" t="n">
-        <v>678994000</v>
+        <v>642002000</v>
       </c>
       <c r="F4" t="n">
-        <v>4042525000</v>
+        <v>4328534000</v>
       </c>
       <c r="G4" t="n">
-        <v>4731898000</v>
+        <v>4973531000</v>
       </c>
       <c r="H4" t="n">
-        <v>2507441000</v>
+        <v>3074434000</v>
       </c>
       <c r="I4" t="n">
-        <v>4042525000</v>
+        <v>4328534000</v>
       </c>
       <c r="J4" t="n">
-        <v>11794000</v>
+        <v>22066000</v>
       </c>
       <c r="K4" t="n">
-        <v>4064698000</v>
+        <v>4353595000</v>
       </c>
       <c r="L4" t="n">
-        <v>4095610000</v>
+        <v>4737092000</v>
       </c>
       <c r="M4" t="n">
-        <v>4115773000</v>
+        <v>4409711000</v>
       </c>
       <c r="N4" t="n">
-        <v>51075000</v>
+        <v>56116000</v>
       </c>
       <c r="O4" t="n">
-        <v>4064698000</v>
+        <v>4353595000</v>
       </c>
       <c r="P4" t="n">
-        <v>-23835000</v>
+        <v>-13763000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1302272000</v>
+        <v>1787999000</v>
       </c>
       <c r="R4" t="n">
-        <v>2712371000</v>
+        <v>2531799000</v>
       </c>
       <c r="S4" t="n">
-        <v>197853000</v>
+        <v>197894000</v>
       </c>
       <c r="T4" t="n">
-        <v>197853000</v>
+        <v>197894000</v>
       </c>
       <c r="U4" t="n">
-        <v>4167327000</v>
+        <v>5624159000</v>
       </c>
       <c r="V4" t="n">
-        <v>64202000</v>
+        <v>601368000</v>
       </c>
       <c r="W4" t="n">
-        <v>18911000</v>
+        <v>200496000</v>
       </c>
       <c r="X4" t="n">
-        <v>9977000</v>
+        <v>3468000</v>
       </c>
       <c r="Y4" t="n">
-        <v>35314000</v>
+        <v>397404000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4402000</v>
+        <v>13907000</v>
       </c>
       <c r="AA4" t="n">
-        <v>30912000</v>
+        <v>383497000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4103125000</v>
+        <v>5022791000</v>
       </c>
       <c r="AC4" t="n">
-        <v>643680000</v>
+        <v>244598000</v>
       </c>
       <c r="AD4" t="n">
-        <v>7392000</v>
+        <v>8159000</v>
       </c>
       <c r="AE4" t="n">
-        <v>636288000</v>
+        <v>236439000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3005421000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>3822106000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>65324000</v>
+        <v>13925000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2940097000</v>
+        <v>3808181000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8283100000</v>
+        <v>10033870000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1672534000</v>
+        <v>1936645000</v>
       </c>
       <c r="AL4" t="n">
-        <v>98265000</v>
+        <v>101264000</v>
       </c>
       <c r="AM4" t="n">
-        <v>11286000</v>
+        <v>8843000</v>
       </c>
       <c r="AN4" t="n">
-        <v>42588000</v>
+        <v>41897000</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>42588000</v>
+        <v>41897000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7922000</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>7922000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>22173000</v>
+        <v>25061000</v>
       </c>
       <c r="AT4" t="n">
-        <v>22173000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>25061000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>1490300000</v>
+        <v>1759580000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1717338000</v>
+        <v>-1831484000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3207638000</v>
+        <v>3591064000</v>
       </c>
       <c r="AY4" t="n">
-        <v>885713000</v>
+        <v>22035000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>152099000</v>
+        <v>172567000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1804769000</v>
+        <v>2638682000</v>
       </c>
       <c r="BB4" t="n">
-        <v>31822000</v>
+        <v>37385000</v>
       </c>
       <c r="BC4" t="n">
-        <v>333235000</v>
+        <v>720395000</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>6610566000</v>
+        <v>8097225000</v>
       </c>
       <c r="BF4" t="n">
-        <v>23449000</v>
+        <v>47546000</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>55884000</v>
       </c>
       <c r="BH4" t="n">
-        <v>61704000</v>
+        <v>60242000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1568001000</v>
+        <v>1947101000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>649308000</v>
+        <v>907939000</v>
       </c>
       <c r="BK4" t="n">
-        <v>281089000</v>
+        <v>571548000</v>
       </c>
       <c r="BL4" t="n">
-        <v>637604000</v>
+        <v>467614000</v>
       </c>
       <c r="BM4" t="n">
-        <v>61318000</v>
+        <v>138725000</v>
       </c>
       <c r="BN4" t="n">
-        <v>9510000</v>
+        <v>120161000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2005973000</v>
+        <v>2211401000</v>
       </c>
       <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>2005973000</v>
+        <v>2211401000</v>
       </c>
       <c r="BR4" t="n">
-        <v>2880611000</v>
+        <v>3516165000</v>
       </c>
       <c r="BS4" t="n">
-        <v>61788000</v>
+        <v>15405000</v>
       </c>
       <c r="BT4" t="n">
-        <v>2818823000</v>
+        <v>3500760000</v>
       </c>
       <c r="BU4" t="n">
-        <v>777167000</v>
+        <v>1258701000</v>
       </c>
       <c r="BV4" t="n">
-        <v>2041656000</v>
+        <v>2242059000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12373000</v>
+      </c>
       <c r="C5" t="n">
-        <v>736155000</v>
+        <v>779202204</v>
       </c>
       <c r="D5" t="n">
-        <v>736155000</v>
+        <v>791575204</v>
       </c>
       <c r="E5" t="n">
-        <v>22555000</v>
+        <v>410692000</v>
       </c>
       <c r="F5" t="n">
-        <v>2982480000</v>
+        <v>4505858000</v>
       </c>
       <c r="G5" t="n">
-        <v>3032424000</v>
+        <v>4911072000</v>
       </c>
       <c r="H5" t="n">
-        <v>2685133000</v>
+        <v>2695701000</v>
       </c>
       <c r="I5" t="n">
-        <v>2982480000</v>
+        <v>4505858000</v>
       </c>
       <c r="J5" t="n">
-        <v>22555000</v>
+        <v>34906000</v>
       </c>
       <c r="K5" t="n">
-        <v>3032424000</v>
+        <v>4535286000</v>
       </c>
       <c r="L5" t="n">
-        <v>3032424000</v>
+        <v>4705750000</v>
       </c>
       <c r="M5" t="n">
-        <v>3345625000</v>
+        <v>4600495000</v>
       </c>
       <c r="N5" t="n">
-        <v>313201000</v>
+        <v>65209000</v>
       </c>
       <c r="O5" t="n">
-        <v>3032424000</v>
+        <v>4535286000</v>
       </c>
       <c r="P5" t="n">
-        <v>-33609000</v>
+        <v>-15652000</v>
       </c>
       <c r="Q5" t="n">
-        <v>680322000</v>
+        <v>2159062000</v>
       </c>
       <c r="R5" t="n">
-        <v>2030037000</v>
+        <v>2382139000</v>
       </c>
       <c r="S5" t="n">
-        <v>184039000</v>
+        <v>197894000</v>
       </c>
       <c r="T5" t="n">
-        <v>184039000</v>
+        <v>197894000</v>
       </c>
       <c r="U5" t="n">
-        <v>2197539000</v>
+        <v>6864447000</v>
       </c>
       <c r="V5" t="n">
-        <v>29486000</v>
+        <v>364846000</v>
       </c>
       <c r="W5" t="n">
-        <v>5279000</v>
+        <v>171821000</v>
       </c>
       <c r="X5" t="n">
-        <v>13165000</v>
+        <v>2448000</v>
       </c>
       <c r="Y5" t="n">
-        <v>11042000</v>
+        <v>190577000</v>
       </c>
       <c r="Z5" t="n">
-        <v>11042000</v>
+        <v>20113000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>170464000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2168053000</v>
+        <v>6499601000</v>
       </c>
       <c r="AC5" t="n">
-        <v>11513000</v>
+        <v>220115000</v>
       </c>
       <c r="AD5" t="n">
-        <v>11513000</v>
+        <v>14793000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>205322000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1669335000</v>
+        <v>5390498000</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>17476000</v>
+        <v>23272000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1651859000</v>
+        <v>5367226000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5543164000</v>
+        <v>11464942000</v>
       </c>
       <c r="AK5" t="n">
-        <v>689978000</v>
+        <v>2269640000</v>
       </c>
       <c r="AL5" t="n">
-        <v>15332000</v>
+        <v>38822000</v>
       </c>
       <c r="AM5" t="n">
-        <v>654000</v>
+        <v>59718000</v>
       </c>
       <c r="AN5" t="n">
-        <v>40614000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>40186000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>38486000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>49944000</v>
+        <v>29428000</v>
       </c>
       <c r="AT5" t="n">
-        <v>38457000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>11487000</v>
-      </c>
+        <v>29428000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>583434000</v>
+        <v>2060385000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1679395000</v>
+        <v>-1770004000</v>
       </c>
       <c r="AX5" t="n">
-        <v>2262829000</v>
+        <v>3830389000</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>124578000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>206626000</v>
+        <v>172741000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1732858000</v>
+        <v>2722861000</v>
       </c>
       <c r="BB5" t="n">
-        <v>31571000</v>
+        <v>51828000</v>
       </c>
       <c r="BC5" t="n">
-        <v>291774000</v>
+        <v>758381000</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>4853186000</v>
+        <v>9195302000</v>
       </c>
       <c r="BF5" t="n">
-        <v>50180000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+        <v>48717000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>147326000</v>
+      </c>
       <c r="BH5" t="n">
-        <v>51324000</v>
+        <v>104656000</v>
       </c>
       <c r="BI5" t="n">
-        <v>832617000</v>
+        <v>1778379000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>416455000</v>
+        <v>790882000</v>
       </c>
       <c r="BK5" t="n">
-        <v>128402000</v>
+        <v>409565000</v>
       </c>
       <c r="BL5" t="n">
-        <v>287760000</v>
+        <v>577932000</v>
       </c>
       <c r="BM5" t="n">
-        <v>26607000</v>
+        <v>57587000</v>
       </c>
       <c r="BN5" t="n">
-        <v>4740000</v>
+        <v>229354000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1616233000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-10642000</v>
-      </c>
+        <v>2895566000</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>1616233000</v>
+        <v>2895566000</v>
       </c>
       <c r="BR5" t="n">
-        <v>2271485000</v>
+        <v>3933717000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4367000</v>
+        <v>1233576000</v>
       </c>
       <c r="BT5" t="n">
-        <v>2267118000</v>
+        <v>2700141000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>671473000</v>
       </c>
       <c r="BV5" t="n">
-        <v>2267118000</v>
+        <v>2028668000</v>
       </c>
     </row>
   </sheetData>
@@ -2849,616 +2849,616 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>880308000</v>
+        <v>410964000</v>
       </c>
       <c r="C2" t="n">
-        <v>-516354000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>275316000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>-21223000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-253798000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2267118000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1627531000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19162000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>620425000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>210135000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>280000000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-915000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-36302000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-36302000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-21223000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-21223000</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>-576380000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2700141000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3500760000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-44382000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-756237000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-430154000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-9172000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-15362000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-149660000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-149660000</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>-241038000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-241038000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-516354000</v>
-      </c>
       <c r="U2" t="n">
-        <v>275316000</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-1782771000</v>
+        <v>-254472000</v>
       </c>
       <c r="W2" t="n">
-        <v>-132543000</v>
+        <v>2495000</v>
       </c>
       <c r="X2" t="n">
-        <v>107156000</v>
+        <v>25668000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1208116000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>-33505000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10859000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-6552396000</v>
+        <v>-44364000</v>
       </c>
       <c r="AB2" t="n">
-        <v>26765000</v>
+        <v>3722000</v>
       </c>
       <c r="AC2" t="n">
-        <v>26765000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>3722000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-8659000</v>
+        <v>-7039000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8659000</v>
+        <v>-7039000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-567374000</v>
+        <v>-245813000</v>
       </c>
       <c r="AH2" t="n">
-        <v>347000</v>
+        <v>946000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-567721000</v>
+        <v>-246759000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1456688000</v>
+        <v>664762000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-61843000</v>
+        <v>-10172000</v>
       </c>
       <c r="AL2" t="n">
-        <v>847614000</v>
+        <v>216867000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1431112000</v>
+        <v>1113590000</v>
       </c>
       <c r="AN2" t="n">
-        <v>135717000</v>
+        <v>-318210000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-719215000</v>
+        <v>-578513000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-121302000</v>
+        <v>-30525000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13374000</v>
+        <v>14789000</v>
       </c>
       <c r="AR2" t="n">
-        <v>248365000</v>
+        <v>163491000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4064000</v>
+        <v>3757000</v>
       </c>
       <c r="AT2" t="n">
-        <v>244301000</v>
+        <v>159734000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-8344000</v>
+        <v>1720000</v>
       </c>
       <c r="AV2" t="n">
-        <v>144033000</v>
+        <v>-44486000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-535000</v>
+        <v>-912000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-26765000</v>
+        <v>2400000</v>
       </c>
       <c r="AY2" t="n">
-        <v>422091000</v>
+        <v>348679000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>677894000</v>
+        <v>-406660000</v>
       </c>
       <c r="C3" t="n">
-        <v>-667200000</v>
+        <v>-83023000</v>
       </c>
       <c r="D3" t="n">
-        <v>619936000</v>
+        <v>776700000</v>
       </c>
       <c r="E3" t="n">
-        <v>330000</v>
+        <v>804111000</v>
       </c>
       <c r="F3" t="n">
-        <v>-508184000</v>
+        <v>-1180656000</v>
       </c>
       <c r="G3" t="n">
-        <v>3500760000</v>
+        <v>2818823000</v>
       </c>
       <c r="H3" t="n">
-        <v>2818823000</v>
+        <v>2267118000</v>
       </c>
       <c r="I3" t="n">
-        <v>-16571000</v>
+        <v>-150568000</v>
       </c>
       <c r="J3" t="n">
-        <v>698508000</v>
+        <v>702273000</v>
       </c>
       <c r="K3" t="n">
-        <v>-263467000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>1097970000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-267033000</v>
+      </c>
       <c r="M3" t="n">
-        <v>-25220000</v>
+        <v>-12361000</v>
       </c>
       <c r="N3" t="n">
-        <v>-180964000</v>
+        <v>-109284000</v>
       </c>
       <c r="O3" t="n">
-        <v>-180964000</v>
+        <v>-109284000</v>
       </c>
       <c r="P3" t="n">
-        <v>330000</v>
+        <v>804111000</v>
       </c>
       <c r="Q3" t="n">
-        <v>330000</v>
+        <v>804111000</v>
       </c>
       <c r="R3" t="n">
-        <v>-47264000</v>
+        <v>693677000</v>
       </c>
       <c r="S3" t="n">
-        <v>-47264000</v>
+        <v>693677000</v>
       </c>
       <c r="T3" t="n">
-        <v>-667200000</v>
+        <v>-83023000</v>
       </c>
       <c r="U3" t="n">
-        <v>619936000</v>
+        <v>776700000</v>
       </c>
       <c r="V3" t="n">
-        <v>-224103000</v>
+        <v>-1169693000</v>
       </c>
       <c r="W3" t="n">
-        <v>146058000</v>
+        <v>33324000</v>
       </c>
       <c r="X3" t="n">
-        <v>89984000</v>
+        <v>49527000</v>
       </c>
       <c r="Y3" t="n">
-        <v>46318000</v>
+        <v>-60309000</v>
       </c>
       <c r="Z3" t="n">
-        <v>61723000</v>
+        <v>3124000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-15405000</v>
+        <v>-63433000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-14822000</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-14822000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6125000</v>
+        <v>-4394000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-6125000</v>
+        <v>-4394000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-500338000</v>
+        <v>-1173019000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1721000</v>
+        <v>3243000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-502059000</v>
+        <v>-1176262000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1186078000</v>
+        <v>773996000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-120805000</v>
+        <v>-59664000</v>
       </c>
       <c r="AL3" t="n">
-        <v>563737000</v>
+        <v>-193859000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1309178000</v>
+        <v>1164944000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-398345000</v>
+        <v>-818948000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-347096000</v>
+        <v>-539855000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-116584000</v>
+        <v>-50685000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20385000</v>
+        <v>22590000</v>
       </c>
       <c r="AR3" t="n">
-        <v>205263000</v>
+        <v>171068000</v>
       </c>
       <c r="AS3" t="n">
-        <v>3153000</v>
+        <v>5298000</v>
       </c>
       <c r="AT3" t="n">
-        <v>202110000</v>
+        <v>165770000</v>
       </c>
       <c r="AU3" t="n">
-        <v>716000</v>
+        <v>736000</v>
       </c>
       <c r="AV3" t="n">
-        <v>90571000</v>
+        <v>226689000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1708000</v>
+        <v>-884000</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>-98000</v>
       </c>
       <c r="AY3" t="n">
-        <v>540032000</v>
+        <v>657647000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-406660000</v>
+        <v>677894000</v>
       </c>
       <c r="C4" t="n">
-        <v>-83023000</v>
+        <v>-667200000</v>
       </c>
       <c r="D4" t="n">
-        <v>776700000</v>
+        <v>619936000</v>
       </c>
       <c r="E4" t="n">
-        <v>804111000</v>
+        <v>330000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1180656000</v>
+        <v>-508184000</v>
       </c>
       <c r="G4" t="n">
+        <v>3500760000</v>
+      </c>
+      <c r="H4" t="n">
         <v>2818823000</v>
       </c>
-      <c r="H4" t="n">
-        <v>2267118000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-150568000</v>
+        <v>-16571000</v>
       </c>
       <c r="J4" t="n">
-        <v>702273000</v>
+        <v>698508000</v>
       </c>
       <c r="K4" t="n">
-        <v>1097970000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-267033000</v>
-      </c>
+        <v>-263467000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-12361000</v>
+        <v>-25220000</v>
       </c>
       <c r="N4" t="n">
-        <v>-109284000</v>
+        <v>-180964000</v>
       </c>
       <c r="O4" t="n">
-        <v>-109284000</v>
+        <v>-180964000</v>
       </c>
       <c r="P4" t="n">
-        <v>804111000</v>
+        <v>330000</v>
       </c>
       <c r="Q4" t="n">
-        <v>804111000</v>
+        <v>330000</v>
       </c>
       <c r="R4" t="n">
-        <v>693677000</v>
+        <v>-47264000</v>
       </c>
       <c r="S4" t="n">
-        <v>693677000</v>
+        <v>-47264000</v>
       </c>
       <c r="T4" t="n">
-        <v>-83023000</v>
+        <v>-667200000</v>
       </c>
       <c r="U4" t="n">
-        <v>776700000</v>
+        <v>619936000</v>
       </c>
       <c r="V4" t="n">
-        <v>-1169693000</v>
+        <v>-224103000</v>
       </c>
       <c r="W4" t="n">
-        <v>33324000</v>
+        <v>146058000</v>
       </c>
       <c r="X4" t="n">
-        <v>49527000</v>
+        <v>89984000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-60309000</v>
+        <v>46318000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3124000</v>
+        <v>61723000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-63433000</v>
+        <v>-15405000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-14822000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-14822000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-4394000</v>
+        <v>-6125000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4394000</v>
+        <v>-6125000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1173019000</v>
+        <v>-500338000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3243000</v>
+        <v>1721000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1176262000</v>
+        <v>-502059000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>773996000</v>
+        <v>1186078000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-59664000</v>
+        <v>-120805000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-193859000</v>
+        <v>563737000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1164944000</v>
+        <v>1309178000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-818948000</v>
+        <v>-398345000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-539855000</v>
+        <v>-347096000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-50685000</v>
+        <v>-116584000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22590000</v>
+        <v>20385000</v>
       </c>
       <c r="AR4" t="n">
-        <v>171068000</v>
+        <v>205263000</v>
       </c>
       <c r="AS4" t="n">
-        <v>5298000</v>
+        <v>3153000</v>
       </c>
       <c r="AT4" t="n">
-        <v>165770000</v>
+        <v>202110000</v>
       </c>
       <c r="AU4" t="n">
-        <v>736000</v>
+        <v>716000</v>
       </c>
       <c r="AV4" t="n">
-        <v>226689000</v>
+        <v>90571000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-884000</v>
+        <v>-1708000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-98000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>657647000</v>
+        <v>540032000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>410964000</v>
+        <v>880308000</v>
       </c>
       <c r="C5" t="n">
+        <v>-516354000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>275316000</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
+        <v>-576380000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2700141000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3500760000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-44382000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-756237000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-430154000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-9172000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-15362000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-149660000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-149660000</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>-21223000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-253798000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2267118000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1627531000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>19162000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>620425000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>210135000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>280000000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-915000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-36302000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-36302000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-21223000</v>
-      </c>
       <c r="Q5" t="n">
-        <v>-21223000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-241038000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-241038000</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-516354000</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>275316000</v>
       </c>
       <c r="V5" t="n">
-        <v>-254472000</v>
+        <v>-1782771000</v>
       </c>
       <c r="W5" t="n">
-        <v>2495000</v>
+        <v>-132543000</v>
       </c>
       <c r="X5" t="n">
-        <v>25668000</v>
+        <v>107156000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-33505000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10859000</v>
-      </c>
+        <v>-1208116000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-44364000</v>
+        <v>-6552396000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3722000</v>
+        <v>26765000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3722000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>26765000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-7039000</v>
+        <v>-8659000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7039000</v>
+        <v>-8659000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-245813000</v>
+        <v>-567374000</v>
       </c>
       <c r="AH5" t="n">
-        <v>946000</v>
+        <v>347000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-246759000</v>
+        <v>-567721000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>664762000</v>
+        <v>1456688000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-10172000</v>
+        <v>-61843000</v>
       </c>
       <c r="AL5" t="n">
-        <v>216867000</v>
+        <v>847614000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1113590000</v>
+        <v>1431112000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-318210000</v>
+        <v>135717000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-578513000</v>
+        <v>-719215000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-30525000</v>
+        <v>-121302000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14789000</v>
+        <v>13374000</v>
       </c>
       <c r="AR5" t="n">
-        <v>163491000</v>
+        <v>248365000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3757000</v>
+        <v>4064000</v>
       </c>
       <c r="AT5" t="n">
-        <v>159734000</v>
+        <v>244301000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1720000</v>
+        <v>-8344000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-44486000</v>
+        <v>144033000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-912000</v>
+        <v>-535000</v>
       </c>
       <c r="AX5" t="n">
-        <v>2400000</v>
+        <v>-26765000</v>
       </c>
       <c r="AY5" t="n">
-        <v>348679000</v>
+        <v>422091000</v>
       </c>
     </row>
   </sheetData>
@@ -3472,7 +3472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FA2"/>
+  <dimension ref="A1:FC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3913,350 +3913,360 @@
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4361,34 +4371,34 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>4.74</v>
+        <v>4.13</v>
       </c>
       <c r="W2" t="n">
-        <v>4.74</v>
+        <v>4.16</v>
       </c>
       <c r="X2" t="n">
-        <v>4.73</v>
+        <v>4.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.9</v>
+        <v>4.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.74</v>
+        <v>4.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.74</v>
+        <v>4.16</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.73</v>
+        <v>4.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.9</v>
+        <v>4.22</v>
       </c>
       <c r="AD2" t="n">
         <v>0.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.21</v>
+        <v>3.69</v>
       </c>
       <c r="AF2" t="n">
         <v>1783036800</v>
@@ -4400,34 +4410,34 @@
         <v>2.37</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.49</v>
+        <v>0.497</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.818182</v>
+        <v>9.431818</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.8697777</v>
+        <v>5.989407</v>
       </c>
       <c r="AL2" t="n">
-        <v>3092000</v>
+        <v>2803000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3092000</v>
+        <v>2803000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2133831</v>
+        <v>2447625</v>
       </c>
       <c r="AO2" t="n">
-        <v>5504011</v>
+        <v>3248511</v>
       </c>
       <c r="AP2" t="n">
-        <v>5504011</v>
+        <v>3248511</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.75</v>
+        <v>4.16</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.76</v>
+        <v>4.21</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -4436,10 +4446,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3668623616</v>
+        <v>3198484992</v>
       </c>
       <c r="AV2" t="n">
-        <v>3668623411</v>
+        <v>3183070312</v>
       </c>
       <c r="AW2" t="n">
         <v>3.92</v>
@@ -4454,19 +4464,19 @@
         <v>1.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2628462</v>
+        <v>0.22916214</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3462</v>
+        <v>4.469</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9815</v>
+        <v>4.8443</v>
       </c>
       <c r="BD2" t="n">
         <v>0.153</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.032278482</v>
+        <v>0.037046004</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -4477,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>-499283040</v>
+        <v>-982143872</v>
       </c>
       <c r="BI2" t="n">
         <v>0.02474</v>
@@ -4492,7 +4502,7 @@
         <v>0.0051599997</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57537</v>
+        <v>0.57553</v>
       </c>
       <c r="BN2" t="n">
         <v>770719204</v>
@@ -4501,7 +4511,7 @@
         <v>6.075</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.7835392</v>
+        <v>0.6831275999999999</v>
       </c>
       <c r="BQ2" t="n">
         <v>1767139200</v>
@@ -4525,16 +4535,16 @@
         <v>0.69289</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.036</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>-1.06</v>
+        <v>-2.085</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.17421603</v>
+        <v>-0.3935389</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CB2" t="n">
         <v>0.153</v>
@@ -4548,7 +4558,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>4.76</v>
+        <v>4.15</v>
       </c>
       <c r="CF2" t="n">
         <v>8.4</v>
@@ -4557,259 +4567,267 @@
         <v>4.6</v>
       </c>
       <c r="CH2" t="n">
-        <v>6.5</v>
+        <v>6.375</v>
       </c>
       <c r="CI2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CK2" t="n">
-        <v>3</v>
+        <v>6.25</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
       </c>
       <c r="CL2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CM2" t="n">
         <v>4667231232</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>5.896</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>471159008</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>337108000</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>1.107</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>1.397</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>13957301248</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>6.919</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>17.723</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.01273</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>0.072129995</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>2448160000</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
         <v>593183488</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="CZ2" t="n">
         <v>797948992</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
         <v>-0.246</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DB2" t="n">
         <v>-0.001</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>0.1754</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>0.03376</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DE2" t="n">
         <v>0.01947</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>0710.HK</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DK2" t="b">
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>finmb_36158</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DU2" t="n">
+        <v>7.372011</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.31899977</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.07138057</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.6942997</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.14332302</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>1.8 - Buy</t>
+        </is>
+      </c>
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>[{'header': 'Dividend', 'message': '0710.HK announced a cash dividend of HKD 0.153 with an ex-date of Jul. 3, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1783008000000, 'amount': '0.153'}}]</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>BOE VARITRONIX</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>BOE Varitronix Limited</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>946949400000</v>
       </c>
-      <c r="DO2" t="n">
-        <v>0.020000458</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>4.73 - 4.9</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="EK2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>4.01 - 4.22</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DR2" t="n">
-        <v>2133831</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.8400001499999999</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.21428575</v>
-      </c>
-      <c r="DU2" t="inlineStr">
+      <c r="EN2" t="n">
+        <v>2447625</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0.23000002</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.058673475</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>3.92 - 8.83</t>
         </is>
       </c>
-      <c r="DV2" t="n">
-        <v>-4.0699997</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.46092862</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-17.421604</v>
-      </c>
-      <c r="DY2" t="n">
+      <c r="ER2" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-0.5300113</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-39.35389</v>
+      </c>
+      <c r="EU2" t="n">
         <v>1742984424</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EV2" t="n">
         <v>1742984424</v>
       </c>
-      <c r="EA2" t="b">
+      <c r="EW2" t="b">
         <v>0</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="EX2" t="n">
         <v>0.44</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EY2" t="n">
         <v>0.69289</v>
       </c>
-      <c r="ED2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>10.577779</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.41380024</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.095209666</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.22149992</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.044464502</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.42195058</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>BOE VARITRONIX</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>BOE Varitronix Limited</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>finmb_36158</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EX2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FA2" t="inlineStr"/>
+      <c r="EZ2" t="n">
+        <v>0.56294</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>0.484261</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="FC2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
